--- a/Data kalibrasi Kelembapan/data.xlsx
+++ b/Data kalibrasi Kelembapan/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nopi cakep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A805E39-F19B-48BC-BDF3-1C3B17B53D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5AEEBC-C4DC-44B0-845B-52275D250A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4365" yWindow="4365" windowWidth="21600" windowHeight="11835" xr2:uid="{59869EFD-B8F9-4126-A57A-37F12D9EE8E8}"/>
   </bookViews>
@@ -427,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FB3E457-C303-426A-8125-168E554946F4}">
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1492,11 +1492,11 @@
         <v>56</v>
       </c>
       <c r="C67">
-        <f t="shared" ref="C67:C100" si="2">100-ABS((B67-A67)/A67)*100</f>
+        <f t="shared" ref="C67:C101" si="2">100-ABS((B67-A67)/A67)*100</f>
         <v>92.307692307692307</v>
       </c>
       <c r="D67">
-        <f t="shared" ref="D67:D100" si="3">ABS((B67-A67)/A67)*100</f>
+        <f t="shared" ref="D67:D101" si="3">ABS((B67-A67)/A67)*100</f>
         <v>7.6923076923076925</v>
       </c>
     </row>
@@ -2024,6 +2024,22 @@
         <v>100</v>
       </c>
       <c r="D100">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>59</v>
+      </c>
+      <c r="B101">
+        <v>59</v>
+      </c>
+      <c r="C101">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="D101">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
